--- a/data/raw/Book1.xlsx
+++ b/data/raw/Book1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Khushi\my trade\data\raw\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FDB67A21-FDAB-45D7-A51D-38E44B9CBD3D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CAC41451-2DC1-4D19-9FE7-12DE4A0032F7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" firstSheet="4" activeTab="4" xr2:uid="{A1FA5CC5-E2C2-4F51-9BAE-3F5476477926}"/>
+    <workbookView xWindow="0" yWindow="360" windowWidth="19420" windowHeight="10300" firstSheet="4" activeTab="4" xr2:uid="{A1FA5CC5-E2C2-4F51-9BAE-3F5476477926}"/>
   </bookViews>
   <sheets>
     <sheet name="Detail1" sheetId="15" r:id="rId1"/>
@@ -47,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="749" uniqueCount="297">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="767" uniqueCount="302">
   <si>
     <t>S No.</t>
   </si>
@@ -938,6 +938,21 @@
   </si>
   <si>
     <t>Count of days</t>
+  </si>
+  <si>
+    <t>VODAFONE  IDEA</t>
+  </si>
+  <si>
+    <t>SUPREME PETROCHEM</t>
+  </si>
+  <si>
+    <t>BEL</t>
+  </si>
+  <si>
+    <t>GE VERNOVA</t>
+  </si>
+  <si>
+    <t>ARVIND FASHION</t>
   </si>
 </sst>
 </file>
@@ -961,7 +976,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -986,6 +1001,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -999,7 +1020,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
@@ -1012,19 +1033,12 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="14" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="4">
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFF00"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="3">
     <dxf>
       <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
     </dxf>
@@ -5686,7 +5700,7 @@
     <tableColumn id="1" xr3:uid="{43186A7E-C90F-4122-810F-22663576FFF9}" name="S No."/>
     <tableColumn id="2" xr3:uid="{9E323C2A-23E3-447D-8702-221DCB1A0BEC}" name="STOCK NAME"/>
     <tableColumn id="3" xr3:uid="{55604429-F8A2-4F2D-BDD7-399C94E5388B}" name="Idea Type"/>
-    <tableColumn id="4" xr3:uid="{4135904D-56D6-4748-AB35-F71A97B8FA7A}" name="Day when told" dataDxfId="3"/>
+    <tableColumn id="4" xr3:uid="{4135904D-56D6-4748-AB35-F71A97B8FA7A}" name="Day when told" dataDxfId="2"/>
     <tableColumn id="5" xr3:uid="{2E9979B2-5DEC-447C-9C89-2177954761BC}" name="Current price"/>
     <tableColumn id="6" xr3:uid="{0DC67F4B-AFFC-49DF-90DE-D84E4BF50859}" name="Target price"/>
     <tableColumn id="7" xr3:uid="{A908147A-56D4-408F-A231-990FCE82EB5F}" name="Stop loss"/>
@@ -5708,7 +5722,7 @@
     <tableColumn id="1" xr3:uid="{0FE28B3C-3AB7-4BE0-B7AC-96CF9B2747F0}" name="S No."/>
     <tableColumn id="2" xr3:uid="{D2527260-1F3C-440C-939F-D930DA527821}" name="STOCK NAME"/>
     <tableColumn id="3" xr3:uid="{8246E459-5157-451A-9FAC-31083D1345B1}" name="Idea Type"/>
-    <tableColumn id="4" xr3:uid="{93C55762-0F03-414D-99E0-97ACF4FA7DFA}" name="Day when told" dataDxfId="2"/>
+    <tableColumn id="4" xr3:uid="{93C55762-0F03-414D-99E0-97ACF4FA7DFA}" name="Day when told" dataDxfId="1"/>
     <tableColumn id="5" xr3:uid="{81ED39E5-3493-4493-A78C-D6A5ABA57C26}" name="Current price"/>
     <tableColumn id="6" xr3:uid="{59D9B7EF-FECD-4742-B24A-99448EFCDD93}" name="Target price"/>
     <tableColumn id="7" xr3:uid="{883CF9A4-9A9F-44D0-A8AC-EA38AA47F33F}" name="Stop loss"/>
@@ -5730,7 +5744,7 @@
     <tableColumn id="1" xr3:uid="{8B8B8DD6-708D-4C5F-B37B-B81570DCF4EE}" name="S No."/>
     <tableColumn id="2" xr3:uid="{02B44AF0-C8B8-48A3-8BB8-4299339D9C30}" name="STOCK NAME"/>
     <tableColumn id="3" xr3:uid="{93865396-7357-48D6-82DA-869641B7D9FB}" name="Idea Type"/>
-    <tableColumn id="4" xr3:uid="{7C72EDB9-51D0-4BAE-BA7C-B7C9EA3DCD3F}" name="Day when told" dataDxfId="1"/>
+    <tableColumn id="4" xr3:uid="{7C72EDB9-51D0-4BAE-BA7C-B7C9EA3DCD3F}" name="Day when told" dataDxfId="0"/>
     <tableColumn id="5" xr3:uid="{186B6608-DC2A-4C46-BF5D-69530C91A937}" name="Current price"/>
     <tableColumn id="6" xr3:uid="{F01039C9-4762-4B7A-9F5B-620F3F465693}" name="Target price"/>
     <tableColumn id="7" xr3:uid="{F60B2394-8080-4885-AA7D-24D499FE396D}" name="Stop loss"/>
@@ -10112,7 +10126,7 @@
         <v>3130</v>
       </c>
     </row>
-    <row r="127" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="127" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A127">
         <v>126</v>
       </c>
@@ -10270,7 +10284,7 @@
         <v>421</v>
       </c>
     </row>
-    <row r="136" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="136" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A136">
         <v>135</v>
       </c>
@@ -10681,7 +10695,7 @@
         <v>1826</v>
       </c>
     </row>
-    <row r="158" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="158" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A158">
         <v>157</v>
       </c>
@@ -10711,7 +10725,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="159" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="159" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A159">
         <v>158</v>
       </c>
@@ -10911,7 +10925,7 @@
         <v>46220</v>
       </c>
     </row>
-    <row r="170" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="170" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A170">
         <v>169</v>
       </c>
@@ -10939,7 +10953,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="171" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="171" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A171">
         <v>170</v>
       </c>
@@ -11102,7 +11116,7 @@
         <v>2260</v>
       </c>
     </row>
-    <row r="180" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="180" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A180">
         <v>179</v>
       </c>
@@ -11186,7 +11200,7 @@
         <v>12096</v>
       </c>
     </row>
-    <row r="185" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="185" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A185">
         <v>184</v>
       </c>
@@ -11372,7 +11386,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="196" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="196" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A196">
         <v>195</v>
       </c>
@@ -11722,7 +11736,7 @@
         <v>1200</v>
       </c>
     </row>
-    <row r="215" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="215" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A215">
         <v>214</v>
       </c>
@@ -11985,7 +11999,7 @@
         <v>46233</v>
       </c>
     </row>
-    <row r="229" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="229" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A229">
         <v>228</v>
       </c>
@@ -12102,7 +12116,7 @@
         <v>910</v>
       </c>
     </row>
-    <row r="236" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="236" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A236">
         <v>235</v>
       </c>
@@ -12238,7 +12252,7 @@
         <v>6610</v>
       </c>
     </row>
-    <row r="243" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="243" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A243">
         <v>243</v>
       </c>
@@ -12316,7 +12330,7 @@
         <v>46239</v>
       </c>
     </row>
-    <row r="248" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="248" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A248">
         <v>248</v>
       </c>
@@ -12500,7 +12514,7 @@
         <v>1192</v>
       </c>
     </row>
-    <row r="258" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="258" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A258">
         <v>259</v>
       </c>
@@ -12597,7 +12611,7 @@
         <v>1088</v>
       </c>
     </row>
-    <row r="264" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="264" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A264">
         <v>265</v>
       </c>
@@ -12663,7 +12677,7 @@
         <v>248</v>
       </c>
     </row>
-    <row r="268" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="268" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A268">
         <v>269</v>
       </c>
@@ -12765,7 +12779,7 @@
         <v>228.8</v>
       </c>
     </row>
-    <row r="273" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="273" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A273">
         <v>274</v>
       </c>
@@ -12871,7 +12885,7 @@
         <v>2900</v>
       </c>
     </row>
-    <row r="279" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="279" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A279">
         <v>280</v>
       </c>
@@ -12983,7 +12997,7 @@
         <v>1600</v>
       </c>
     </row>
-    <row r="285" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="285" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A285">
         <v>286</v>
       </c>
@@ -13052,7 +13066,7 @@
         <v>1110</v>
       </c>
     </row>
-    <row r="289" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="289" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A289">
         <v>290</v>
       </c>
@@ -13069,7 +13083,7 @@
         <v>705</v>
       </c>
     </row>
-    <row r="290" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="290" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A290">
         <v>291</v>
       </c>
@@ -13314,7 +13328,7 @@
         <v>1398</v>
       </c>
     </row>
-    <row r="304" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="304" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A304">
         <v>305</v>
       </c>
@@ -13433,7 +13447,7 @@
         <v>573</v>
       </c>
     </row>
-    <row r="310" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="310" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A310">
         <v>311</v>
       </c>
@@ -13497,7 +13511,7 @@
         <v>13.7</v>
       </c>
     </row>
-    <row r="313" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="313" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A313">
         <v>314</v>
       </c>
@@ -13663,7 +13677,7 @@
         <v>1217</v>
       </c>
     </row>
-    <row r="322" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="322" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A322">
         <v>323</v>
       </c>
@@ -13798,7 +13812,7 @@
         <v>397</v>
       </c>
     </row>
-    <row r="329" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="329" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A329">
         <v>330</v>
       </c>
@@ -13893,7 +13907,7 @@
         <v>358</v>
       </c>
     </row>
-    <row r="334" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="334" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A334">
         <v>335</v>
       </c>
@@ -14006,7 +14020,7 @@
         <v>1514</v>
       </c>
     </row>
-    <row r="340" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="340" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A340">
         <v>341</v>
       </c>
@@ -14098,7 +14112,7 @@
         <v>4420</v>
       </c>
     </row>
-    <row r="345" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="345" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A345">
         <v>346</v>
       </c>
@@ -14216,7 +14230,7 @@
         <v>1887</v>
       </c>
     </row>
-    <row r="351" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="351" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A351">
         <v>352</v>
       </c>
@@ -14365,7 +14379,7 @@
         <v>629</v>
       </c>
     </row>
-    <row r="359" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="359" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A359">
         <v>360</v>
       </c>
@@ -14621,7 +14635,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="372" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="372" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A372">
         <v>373</v>
       </c>
@@ -14716,7 +14730,7 @@
         <v>2310</v>
       </c>
     </row>
-    <row r="377" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="377" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A377">
         <v>378</v>
       </c>
@@ -14819,7 +14833,7 @@
         <v>46267</v>
       </c>
     </row>
-    <row r="383" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="383" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A383">
         <v>384</v>
       </c>
@@ -14900,7 +14914,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="388" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="388" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A388">
         <v>389</v>
       </c>
@@ -15011,113 +15025,312 @@
       <c r="A394">
         <v>395</v>
       </c>
+      <c r="B394" t="s">
+        <v>292</v>
+      </c>
+      <c r="D394" s="1">
+        <v>46272</v>
+      </c>
+      <c r="E394">
+        <v>4856</v>
+      </c>
+      <c r="F394">
+        <v>5800</v>
+      </c>
     </row>
     <row r="395" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A395">
         <v>396</v>
       </c>
+      <c r="B395" t="s">
+        <v>163</v>
+      </c>
+      <c r="D395" s="1">
+        <v>46272</v>
+      </c>
+      <c r="E395">
+        <v>1660</v>
+      </c>
     </row>
     <row r="396" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A396">
         <v>397</v>
       </c>
+      <c r="B396" s="2" t="s">
+        <v>263</v>
+      </c>
+      <c r="C396" s="2"/>
+      <c r="D396" s="9">
+        <v>46272</v>
+      </c>
+      <c r="E396" s="2">
+        <v>418</v>
+      </c>
+      <c r="F396" s="2">
+        <v>442</v>
+      </c>
+      <c r="G396" s="2">
+        <v>406</v>
+      </c>
     </row>
     <row r="397" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A397">
         <v>398</v>
       </c>
+      <c r="B397" t="s">
+        <v>232</v>
+      </c>
+      <c r="D397" s="1">
+        <v>46272</v>
+      </c>
+      <c r="E397">
+        <v>696</v>
+      </c>
+      <c r="F397">
+        <v>900</v>
+      </c>
     </row>
     <row r="398" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A398">
         <v>399</v>
       </c>
+      <c r="B398" s="2" t="s">
+        <v>297</v>
+      </c>
+      <c r="C398" s="2"/>
+      <c r="D398" s="9">
+        <v>46273</v>
+      </c>
+      <c r="E398" s="2">
+        <v>15.6</v>
+      </c>
+      <c r="F398" s="2">
+        <v>16.8</v>
+      </c>
+      <c r="G398" s="2">
+        <v>15</v>
+      </c>
     </row>
     <row r="399" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A399">
         <v>400</v>
       </c>
+      <c r="B399" t="s">
+        <v>182</v>
+      </c>
+      <c r="D399" s="1">
+        <v>46273</v>
+      </c>
+      <c r="E399">
+        <v>2868</v>
+      </c>
     </row>
     <row r="400" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A400">
         <v>401</v>
       </c>
-    </row>
-    <row r="401" spans="1:1" hidden="1" x14ac:dyDescent="0.35">
+      <c r="B400" s="2" t="s">
+        <v>298</v>
+      </c>
+      <c r="C400" s="2" t="s">
+        <v>241</v>
+      </c>
+      <c r="D400" s="9">
+        <v>46273</v>
+      </c>
+      <c r="E400" s="2">
+        <v>802</v>
+      </c>
+      <c r="F400" s="2"/>
+      <c r="G400" s="2"/>
+    </row>
+    <row r="401" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A401">
         <v>402</v>
       </c>
-    </row>
-    <row r="402" spans="1:1" hidden="1" x14ac:dyDescent="0.35">
+      <c r="B401" t="s">
+        <v>299</v>
+      </c>
+      <c r="D401" s="1">
+        <v>46273</v>
+      </c>
+      <c r="E401">
+        <v>405</v>
+      </c>
+      <c r="F401">
+        <v>530</v>
+      </c>
+    </row>
+    <row r="402" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A402">
         <v>403</v>
       </c>
-    </row>
-    <row r="403" spans="1:1" hidden="1" x14ac:dyDescent="0.35">
+      <c r="B402" s="10" t="s">
+        <v>129</v>
+      </c>
+      <c r="D402" s="1">
+        <v>46273</v>
+      </c>
+      <c r="E402">
+        <v>1406</v>
+      </c>
+      <c r="F402">
+        <v>1620</v>
+      </c>
+      <c r="G402">
+        <v>1300</v>
+      </c>
+    </row>
+    <row r="403" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A403">
         <v>404</v>
       </c>
-    </row>
-    <row r="404" spans="1:1" hidden="1" x14ac:dyDescent="0.35">
+      <c r="B403" t="s">
+        <v>300</v>
+      </c>
+      <c r="D403" s="1">
+        <v>46273</v>
+      </c>
+      <c r="E403">
+        <v>4368</v>
+      </c>
+      <c r="F403">
+        <v>5100</v>
+      </c>
+    </row>
+    <row r="404" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A404">
         <v>405</v>
       </c>
-    </row>
-    <row r="405" spans="1:1" hidden="1" x14ac:dyDescent="0.35">
+      <c r="B404" t="s">
+        <v>24</v>
+      </c>
+      <c r="D404" s="1">
+        <v>46273</v>
+      </c>
+      <c r="E404">
+        <v>171</v>
+      </c>
+      <c r="F404">
+        <v>190</v>
+      </c>
+      <c r="G404">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="405" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A405">
         <v>406</v>
       </c>
-    </row>
-    <row r="406" spans="1:1" hidden="1" x14ac:dyDescent="0.35">
+      <c r="B405" t="s">
+        <v>163</v>
+      </c>
+      <c r="D405" s="1">
+        <v>46274</v>
+      </c>
+      <c r="E405">
+        <v>1670</v>
+      </c>
+    </row>
+    <row r="406" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A406">
         <v>407</v>
       </c>
-    </row>
-    <row r="407" spans="1:1" hidden="1" x14ac:dyDescent="0.35">
+      <c r="B406" t="s">
+        <v>292</v>
+      </c>
+      <c r="D406" s="1">
+        <v>46274</v>
+      </c>
+      <c r="E406">
+        <v>4892</v>
+      </c>
+      <c r="F406">
+        <v>5500</v>
+      </c>
+      <c r="G406">
+        <v>4600</v>
+      </c>
+    </row>
+    <row r="407" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A407">
         <v>408</v>
       </c>
-    </row>
-    <row r="408" spans="1:1" hidden="1" x14ac:dyDescent="0.35">
+      <c r="B407" t="s">
+        <v>301</v>
+      </c>
+      <c r="C407" t="s">
+        <v>176</v>
+      </c>
+      <c r="D407" s="1">
+        <v>46274</v>
+      </c>
+      <c r="E407">
+        <v>581</v>
+      </c>
+      <c r="F407">
+        <v>680</v>
+      </c>
+    </row>
+    <row r="408" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A408">
         <v>409</v>
       </c>
-    </row>
-    <row r="409" spans="1:1" hidden="1" x14ac:dyDescent="0.35">
+      <c r="B408" t="s">
+        <v>101</v>
+      </c>
+      <c r="C408" t="s">
+        <v>148</v>
+      </c>
+      <c r="D408" s="1">
+        <v>46274</v>
+      </c>
+      <c r="E408">
+        <v>895</v>
+      </c>
+      <c r="F408">
+        <v>955</v>
+      </c>
+      <c r="G408">
+        <v>865</v>
+      </c>
+    </row>
+    <row r="409" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A409">
         <v>410</v>
       </c>
     </row>
-    <row r="410" spans="1:1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="410" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A410">
         <v>411</v>
       </c>
     </row>
-    <row r="411" spans="1:1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="411" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A411">
         <v>412</v>
       </c>
     </row>
-    <row r="412" spans="1:1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="412" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A412">
         <v>413</v>
       </c>
     </row>
-    <row r="413" spans="1:1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="413" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A413">
         <v>414</v>
       </c>
     </row>
-    <row r="414" spans="1:1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="414" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A414">
         <v>415</v>
       </c>
     </row>
-    <row r="415" spans="1:1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="415" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A415">
         <v>416</v>
       </c>
     </row>
-    <row r="416" spans="1:1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="416" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A416">
         <v>417</v>
       </c>
@@ -15615,7 +15828,9 @@
   </sheetData>
   <autoFilter ref="A1:H514" xr:uid="{11702C7E-E6DA-4340-BEE9-A978C9B55E59}">
     <filterColumn colId="1">
-      <colorFilter dxfId="0"/>
+      <filters>
+        <filter val="LENSKART"/>
+      </filters>
     </filterColumn>
     <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:H514">
       <sortCondition ref="A1:A514"/>

--- a/data/raw/Book1.xlsx
+++ b/data/raw/Book1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Khushi\my trade\data\raw\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{32CB60E8-74ED-4242-B258-F313AE5CB0EE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{925DC34D-441F-46CE-A341-217F36009D58}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" firstSheet="4" activeTab="5" xr2:uid="{A1FA5CC5-E2C2-4F51-9BAE-3F5476477926}"/>
+    <workbookView xWindow="3380" yWindow="10" windowWidth="14520" windowHeight="6390" firstSheet="4" activeTab="5" xr2:uid="{A1FA5CC5-E2C2-4F51-9BAE-3F5476477926}"/>
   </bookViews>
   <sheets>
     <sheet name="Detail1" sheetId="15" r:id="rId1"/>
@@ -48,7 +48,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="830" uniqueCount="323">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="839" uniqueCount="326">
   <si>
     <t>S No.</t>
   </si>
@@ -1017,6 +1017,15 @@
   </si>
   <si>
     <t>DR LAL PATHSLAB</t>
+  </si>
+  <si>
+    <t>MOLBIO DIAGNOSTICS</t>
+  </si>
+  <si>
+    <t>TRENT</t>
+  </si>
+  <si>
+    <t>ENDURANCE TECHNOLOGIES</t>
   </si>
 </sst>
 </file>
@@ -4149,6 +4158,33 @@
                 <c:pt idx="454">
                   <c:v>0</c:v>
                 </c:pt>
+                <c:pt idx="455">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="456">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="457">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="458">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="459">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="460">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="461">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="462">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="463">
+                  <c:v>0</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
@@ -5967,6 +6003,18 @@
                 <c:pt idx="454">
                   <c:v>46300</c:v>
                 </c:pt>
+                <c:pt idx="455">
+                  <c:v>46301</c:v>
+                </c:pt>
+                <c:pt idx="456">
+                  <c:v>46301</c:v>
+                </c:pt>
+                <c:pt idx="457">
+                  <c:v>46301</c:v>
+                </c:pt>
+                <c:pt idx="458">
+                  <c:v>46301</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
@@ -7263,6 +7311,33 @@
                 <c:pt idx="454">
                   <c:v>2005</c:v>
                 </c:pt>
+                <c:pt idx="455">
+                  <c:v>1771</c:v>
+                </c:pt>
+                <c:pt idx="456">
+                  <c:v>1503</c:v>
+                </c:pt>
+                <c:pt idx="457">
+                  <c:v>2580</c:v>
+                </c:pt>
+                <c:pt idx="458">
+                  <c:v>291.14999999999998</c:v>
+                </c:pt>
+                <c:pt idx="459">
+                  <c:v>452</c:v>
+                </c:pt>
+                <c:pt idx="460">
+                  <c:v>2050</c:v>
+                </c:pt>
+                <c:pt idx="461">
+                  <c:v>313</c:v>
+                </c:pt>
+                <c:pt idx="462">
+                  <c:v>2516</c:v>
+                </c:pt>
+                <c:pt idx="463">
+                  <c:v>1160</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
@@ -8150,6 +8225,24 @@
                 </c:pt>
                 <c:pt idx="454">
                   <c:v>2155</c:v>
+                </c:pt>
+                <c:pt idx="455">
+                  <c:v>1879</c:v>
+                </c:pt>
+                <c:pt idx="456">
+                  <c:v>1800</c:v>
+                </c:pt>
+                <c:pt idx="457">
+                  <c:v>3775</c:v>
+                </c:pt>
+                <c:pt idx="458">
+                  <c:v>317.75</c:v>
+                </c:pt>
+                <c:pt idx="459">
+                  <c:v>480</c:v>
+                </c:pt>
+                <c:pt idx="462">
+                  <c:v>3065</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -8659,6 +8752,15 @@
                 </c:pt>
                 <c:pt idx="454">
                   <c:v>1930</c:v>
+                </c:pt>
+                <c:pt idx="455">
+                  <c:v>1717</c:v>
+                </c:pt>
+                <c:pt idx="458">
+                  <c:v>278</c:v>
+                </c:pt>
+                <c:pt idx="459">
+                  <c:v>438</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -24754,118 +24856,211 @@
       <c r="A457">
         <v>458</v>
       </c>
+      <c r="B457" t="s">
+        <v>243</v>
+      </c>
+      <c r="D457" s="1">
+        <v>46301</v>
+      </c>
+      <c r="E457">
+        <v>1771</v>
+      </c>
+      <c r="F457">
+        <v>1879</v>
+      </c>
+      <c r="G457">
+        <v>1717</v>
+      </c>
     </row>
     <row r="458" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A458">
         <v>459</v>
       </c>
+      <c r="B458" t="s">
+        <v>323</v>
+      </c>
+      <c r="D458" s="1">
+        <v>46301</v>
+      </c>
+      <c r="E458">
+        <v>1503</v>
+      </c>
+      <c r="F458">
+        <v>1800</v>
+      </c>
     </row>
     <row r="459" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A459">
         <v>460</v>
       </c>
+      <c r="B459" t="s">
+        <v>324</v>
+      </c>
+      <c r="D459" s="1">
+        <v>46301</v>
+      </c>
+      <c r="E459">
+        <v>2580</v>
+      </c>
+      <c r="F459">
+        <v>3775</v>
+      </c>
     </row>
     <row r="460" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A460">
         <v>461</v>
       </c>
+      <c r="B460" t="s">
+        <v>226</v>
+      </c>
+      <c r="D460" s="1">
+        <v>46301</v>
+      </c>
+      <c r="E460">
+        <v>291.14999999999998</v>
+      </c>
+      <c r="F460">
+        <v>317.75</v>
+      </c>
+      <c r="G460">
+        <v>278</v>
+      </c>
     </row>
     <row r="461" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A461">
         <v>462</v>
       </c>
+      <c r="B461" t="s">
+        <v>27</v>
+      </c>
+      <c r="E461">
+        <v>452</v>
+      </c>
+      <c r="F461">
+        <v>480</v>
+      </c>
+      <c r="G461">
+        <v>438</v>
+      </c>
     </row>
     <row r="462" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A462">
         <v>463</v>
       </c>
+      <c r="B462" t="s">
+        <v>273</v>
+      </c>
+      <c r="E462">
+        <v>2050</v>
+      </c>
     </row>
     <row r="463" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A463">
         <v>464</v>
       </c>
+      <c r="B463" t="s">
+        <v>283</v>
+      </c>
+      <c r="E463">
+        <v>313</v>
+      </c>
     </row>
     <row r="464" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A464">
         <v>465</v>
       </c>
-    </row>
-    <row r="465" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="B464" t="s">
+        <v>325</v>
+      </c>
+      <c r="E464">
+        <v>2516</v>
+      </c>
+      <c r="F464">
+        <v>3065</v>
+      </c>
+    </row>
+    <row r="465" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A465">
         <v>466</v>
       </c>
-    </row>
-    <row r="466" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="B465" t="s">
+        <v>81</v>
+      </c>
+      <c r="E465">
+        <v>1160</v>
+      </c>
+    </row>
+    <row r="466" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A466">
         <v>467</v>
       </c>
     </row>
-    <row r="467" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="467" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A467">
         <v>468</v>
       </c>
     </row>
-    <row r="468" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="468" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A468">
         <v>469</v>
       </c>
     </row>
-    <row r="469" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="469" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A469">
         <v>470</v>
       </c>
     </row>
-    <row r="470" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="470" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A470">
         <v>471</v>
       </c>
     </row>
-    <row r="471" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="471" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A471">
         <v>472</v>
       </c>
     </row>
-    <row r="472" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="472" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A472">
         <v>473</v>
       </c>
     </row>
-    <row r="473" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="473" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A473">
         <v>474</v>
       </c>
     </row>
-    <row r="474" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="474" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A474">
         <v>475</v>
       </c>
     </row>
-    <row r="475" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="475" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A475">
         <v>476</v>
       </c>
     </row>
-    <row r="476" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="476" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A476">
         <v>477</v>
       </c>
     </row>
-    <row r="477" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="477" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A477">
         <v>478</v>
       </c>
     </row>
-    <row r="478" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="478" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A478">
         <v>479</v>
       </c>
     </row>
-    <row r="479" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="479" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A479">
         <v>480</v>
       </c>
     </row>
-    <row r="480" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="480" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A480">
         <v>481</v>
       </c>

--- a/data/raw/Book1.xlsx
+++ b/data/raw/Book1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Khushi\my trade\data\raw\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{925DC34D-441F-46CE-A341-217F36009D58}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CC28943F-F75B-4E7B-B696-95F67C8FCD0E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3380" yWindow="10" windowWidth="14520" windowHeight="6390" firstSheet="4" activeTab="5" xr2:uid="{A1FA5CC5-E2C2-4F51-9BAE-3F5476477926}"/>
+    <workbookView xWindow="0" yWindow="360" windowWidth="19420" windowHeight="10300" firstSheet="4" activeTab="5" xr2:uid="{A1FA5CC5-E2C2-4F51-9BAE-3F5476477926}"/>
   </bookViews>
   <sheets>
     <sheet name="Detail1" sheetId="15" r:id="rId1"/>
@@ -48,7 +48,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="839" uniqueCount="326">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="843" uniqueCount="328">
   <si>
     <t>S No.</t>
   </si>
@@ -1026,6 +1026,12 @@
   </si>
   <si>
     <t>ENDURANCE TECHNOLOGIES</t>
+  </si>
+  <si>
+    <t>NATIONAL ALUMINIUM</t>
+  </si>
+  <si>
+    <t>SENCO GOLD</t>
   </si>
 </sst>
 </file>
@@ -4185,6 +4191,18 @@
                 <c:pt idx="463">
                   <c:v>0</c:v>
                 </c:pt>
+                <c:pt idx="464">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="465">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="466">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="467">
+                  <c:v>0</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
@@ -6015,6 +6033,33 @@
                 <c:pt idx="458">
                   <c:v>46301</c:v>
                 </c:pt>
+                <c:pt idx="459">
+                  <c:v>46302</c:v>
+                </c:pt>
+                <c:pt idx="460">
+                  <c:v>46302</c:v>
+                </c:pt>
+                <c:pt idx="461">
+                  <c:v>46302</c:v>
+                </c:pt>
+                <c:pt idx="462">
+                  <c:v>46302</c:v>
+                </c:pt>
+                <c:pt idx="463">
+                  <c:v>46302</c:v>
+                </c:pt>
+                <c:pt idx="464">
+                  <c:v>46303</c:v>
+                </c:pt>
+                <c:pt idx="465">
+                  <c:v>46303</c:v>
+                </c:pt>
+                <c:pt idx="466">
+                  <c:v>46303</c:v>
+                </c:pt>
+                <c:pt idx="467">
+                  <c:v>46303</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
@@ -7338,6 +7383,18 @@
                 <c:pt idx="463">
                   <c:v>1160</c:v>
                 </c:pt>
+                <c:pt idx="464">
+                  <c:v>322</c:v>
+                </c:pt>
+                <c:pt idx="465">
+                  <c:v>602</c:v>
+                </c:pt>
+                <c:pt idx="466">
+                  <c:v>314</c:v>
+                </c:pt>
+                <c:pt idx="467">
+                  <c:v>321</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
@@ -8243,6 +8300,9 @@
                 </c:pt>
                 <c:pt idx="462">
                   <c:v>3065</c:v>
+                </c:pt>
+                <c:pt idx="466">
+                  <c:v>340</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -24927,21 +24987,26 @@
       </c>
     </row>
     <row r="461" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A461">
+      <c r="A461" s="2">
         <v>462</v>
       </c>
-      <c r="B461" t="s">
+      <c r="B461" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="E461">
+      <c r="C461" s="2"/>
+      <c r="D461" s="9">
+        <v>46302</v>
+      </c>
+      <c r="E461" s="2">
         <v>452</v>
       </c>
-      <c r="F461">
+      <c r="F461" s="2">
         <v>480</v>
       </c>
-      <c r="G461">
+      <c r="G461" s="2">
         <v>438</v>
       </c>
+      <c r="H461" s="2"/>
     </row>
     <row r="462" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A462">
@@ -24950,6 +25015,9 @@
       <c r="B462" t="s">
         <v>273</v>
       </c>
+      <c r="D462" s="1">
+        <v>46302</v>
+      </c>
       <c r="E462">
         <v>2050</v>
       </c>
@@ -24961,6 +25029,9 @@
       <c r="B463" t="s">
         <v>283</v>
       </c>
+      <c r="D463" s="1">
+        <v>46302</v>
+      </c>
       <c r="E463">
         <v>313</v>
       </c>
@@ -24972,6 +25043,9 @@
       <c r="B464" t="s">
         <v>325</v>
       </c>
+      <c r="D464" s="1">
+        <v>46302</v>
+      </c>
       <c r="E464">
         <v>2516</v>
       </c>
@@ -24979,88 +25053,130 @@
         <v>3065</v>
       </c>
     </row>
-    <row r="465" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="465" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A465">
         <v>466</v>
       </c>
       <c r="B465" t="s">
         <v>81</v>
       </c>
+      <c r="D465" s="1">
+        <v>46302</v>
+      </c>
       <c r="E465">
         <v>1160</v>
       </c>
     </row>
-    <row r="466" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="466" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A466">
         <v>467</v>
       </c>
-    </row>
-    <row r="467" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="B466" t="s">
+        <v>326</v>
+      </c>
+      <c r="D466" s="1">
+        <v>46303</v>
+      </c>
+      <c r="E466">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="467" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A467">
         <v>468</v>
       </c>
-    </row>
-    <row r="468" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="B467" t="s">
+        <v>320</v>
+      </c>
+      <c r="D467" s="1">
+        <v>46303</v>
+      </c>
+      <c r="E467">
+        <v>602</v>
+      </c>
+    </row>
+    <row r="468" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A468">
         <v>469</v>
       </c>
-    </row>
-    <row r="469" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="B468" t="s">
+        <v>32</v>
+      </c>
+      <c r="D468" s="1">
+        <v>46303</v>
+      </c>
+      <c r="E468">
+        <v>314</v>
+      </c>
+      <c r="F468">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="469" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A469">
         <v>470</v>
       </c>
-    </row>
-    <row r="470" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="B469" t="s">
+        <v>327</v>
+      </c>
+      <c r="D469" s="1">
+        <v>46303</v>
+      </c>
+      <c r="E469">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="470" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A470">
         <v>471</v>
       </c>
     </row>
-    <row r="471" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="471" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A471">
         <v>472</v>
       </c>
     </row>
-    <row r="472" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="472" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A472">
         <v>473</v>
       </c>
     </row>
-    <row r="473" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="473" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A473">
         <v>474</v>
       </c>
     </row>
-    <row r="474" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="474" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A474">
         <v>475</v>
       </c>
     </row>
-    <row r="475" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="475" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A475">
         <v>476</v>
       </c>
     </row>
-    <row r="476" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="476" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A476">
         <v>477</v>
       </c>
     </row>
-    <row r="477" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="477" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A477">
         <v>478</v>
       </c>
     </row>
-    <row r="478" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="478" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A478">
         <v>479</v>
       </c>
     </row>
-    <row r="479" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="479" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A479">
         <v>480</v>
       </c>
     </row>
-    <row r="480" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="480" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A480">
         <v>481</v>
       </c>
